--- a/www/download/COUNTRY.SWE.rpA1.xlsx
+++ b/www/download/COUNTRY.SWE.rpA1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Suécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>7.1209853786912</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>6.70421035800362</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>7.62718343458456</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>7.94723073282277</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>8.26104914409274</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>9.13075211422837</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>10.3114045632859</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>9.70685325223753</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>8.06776946061647</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>7.33729552481548</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>7.44934438059463</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>7.36702534389249</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>6.75082699066162</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.51703522574423</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.60913399607839</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.129</t>
+          <t>0.00187422018462446</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.096</t>
+          <t>-0.0176905484027334</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.043</t>
+          <t>0.140907973423963</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>0.0722296417293242</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.198</t>
+          <t>0.0637192687761332</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>0.01265888722604</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.391</t>
+          <t>0.0142666679850867</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.393</t>
+          <t>-0.0359939474688956</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.368</t>
+          <t>-0.0724954988469924</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.337</t>
+          <t>-0.117427711592401</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.349</t>
+          <t>-0.137879220311306</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.423</t>
+          <t>-0.122664391512374</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.524</t>
+          <t>-0.131450702456461</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.542</t>
+          <t>-0.0354858540422014</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.425</t>
+          <t>0.106303933188275</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.848</t>
+          <t>0.346504706947899</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.819</t>
+          <t>0.312519657957105</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.768</t>
+          <t>0.512986393774153</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.836</t>
+          <t>0.406284480656395</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.918</t>
+          <t>0.410194781936543</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.023</t>
+          <t>0.311419735786957</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.124</t>
+          <t>0.304454850738159</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.134</t>
+          <t>0.258079740568052</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>0.16557118940932</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.091</t>
+          <t>0.131449275243201</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>0.102611461528128</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.112130376443693</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>0.0906192889190516</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.321</t>
+          <t>0.239434777910275</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.228</t>
+          <t>0.407360057696001</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6772.82</t>
+          <t>0.485664162052157</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6770.69</t>
+          <t>0.464966412714094</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6703.5</t>
+          <t>0.697383582152194</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6809.79</t>
+          <t>0.587312510373466</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6988.38</t>
+          <t>0.601524601148276</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7061.95</t>
+          <t>0.481269380941763</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7105.7</t>
+          <t>0.470857168585027</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7006.6</t>
+          <t>0.424796781381781</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6908.1</t>
+          <t>0.200048491772422</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6963.43</t>
+          <t>0.256741789803466</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6979.96</t>
+          <t>0.216158358328286</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>0.217089269990293</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>7319.33</t>
+          <t>0.140359313656544</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>7362.323</t>
+          <t>0.297239009139861</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7146.911</t>
+          <t>0.50127364043755</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6234.64</t>
+          <t>9880592692.78019</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6244.23</t>
+          <t>9581767136.74591</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6174.71</t>
+          <t>9234511490.77127</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6277.92</t>
+          <t>9599063467.40582</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6444.15</t>
+          <t>9795643820.22805</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6539.08</t>
+          <t>10391999477.2816</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6609.93</t>
+          <t>9833168293.31257</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6527.4</t>
+          <t>9592875012.40764</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6446.22</t>
+          <t>9999722697.60215</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6489.13</t>
+          <t>10364066170.7089</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6490.82</t>
+          <t>10631976878.5638</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6587.61</t>
+          <t>10772474040.7965</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6822.76</t>
+          <t>11307813679.0333</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6920.38</t>
+          <t>10209090188.1298</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6705.67</t>
+          <t>8507639393.28281</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>4836144559.92482</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>4955591791.62743</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>4248213845.2179</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>4634038696.99874</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>4766688908.04856</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>5239529193.85792</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>5334794952.2191</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>5490901651.99126</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>5875842153.3868</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>6080401165.56075</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>6258896447.5244</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>6307546524.51819</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>6691736578.09713</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>6035202453.60704</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>5130118192.59193</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>56.83</t>
+          <t>972878.830947649</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>57.47</t>
+          <t>862283.033849521</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>886901.872392069</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>918915.462590257</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>57.42</t>
+          <t>935380.766056562</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>996027.62838063</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>1012436.10455655</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>915568.900677333</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>798286.822024351</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>710649.065121436</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>695550.024253672</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>642118.265697792</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>573632.564455885</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>56.12</t>
+          <t>473193.339001596</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>470860.326797766</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>30529.227175921</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>30610.5480694473</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>29954.6016071986</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>30186.3303280077</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>32071.0874215819</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>32977.3704144147</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>32392.3737200484</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18.49</t>
+          <t>32797.3003477562</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>34765.1163133721</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>38462.3715502257</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>41038.3022554327</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>43003.8819885326</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>50235.5864930481</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>56290.9916691364</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>50915.0011554671</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>76914.6265402545</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>75146.5877024326</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>71958.2408309707</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>74393.7038292108</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>79064.0247918589</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>85614.6316752692</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>78880.7456702743</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>78667.09747747</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>88338.5949040121</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>100904.578329726</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>110859.418137008</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>117728.821226885</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>139791.330355757</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>139735.284235306</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>108623.779126572</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>0.289175690002637</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>0.260037198895871</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>0.453483799303255</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>0.354740521279186</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>59.43</t>
+          <t>0.351913272360814</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>60.73</t>
+          <t>0.248028163993339</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>60.91</t>
+          <t>0.23902231654667</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>0.188766511168124</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>61.48</t>
+          <t>0.0970716761484878</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>61.25</t>
+          <t>0.0672207019422142</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>0.037055023105125</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>0.0444013332907129</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>0.0195798833940541</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>0.146669072528613</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>0.307118032574667</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>48664.0245698599</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>53484.099109837</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>50572.9831406212</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>52046.5431885725</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>54864.259842949</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>53432.1445377011</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>48358.4082237311</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>52006.600409208</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>62542.9067994847</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>64230.6436042982</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>65520.3671164255</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>67553.0926450966</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>77102.2193546365</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7.1209853786912</t>
+          <t>1256.85964965164</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.70421035800362</t>
+          <t>1297.58105093668</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7.62718343458456</t>
+          <t>1127.445288009</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7.94723073282277</t>
+          <t>1207.94481583785</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.26104914409274</t>
+          <t>1216.73700940483</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.13075211422837</t>
+          <t>1302.42591012899</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10.3114045632859</t>
+          <t>1293.72270642621</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.70685325223753</t>
+          <t>1328.16546175493</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.06776946061647</t>
+          <t>1423.54931519207</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7.33729552481548</t>
+          <t>1486.2145985434</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7.44934438059463</t>
+          <t>1525.36957679967</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.36702534389249</t>
+          <t>1512.45600530361</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>6.75082699066162</t>
+          <t>1567.92253288435</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.51703522574423</t>
+          <t>1396.81126984217</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7.60913399607839</t>
+          <t>1213.27044028762</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>6785659204.69237</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>6841459627.04335</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>6073514458.36313</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>6435233286.15525</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>6725728193.30494</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>7156238318.92549</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>6787239794.72098</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>7226413271.59041</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>8423616332.35382</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>9618856338.46357</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>9527783510.45163</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>9760329002.75927</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>10101539099.8617</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>9355807398.05345</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>7464420270.04687</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>7156247990.29891</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>7270593201.36774</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>6490849871.86974</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>7030961710.44371</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>7353090333.00008</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>7227958950.93166</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>6850094486.09285</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>7198454410.23164</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>8179164501.24362</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>9075890611.97468</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>8761588365.09404</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>8735195598.86459</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>8889496131.02278</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>8177028182.16992</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>6354727051.73621</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>-370588785.606539</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>-429133574.324387</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-417335413.506607</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>-595728424.288462</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-627362139.695144</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-71720632.0061687</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>-62854691.3718652</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>27958861.3587787</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>244451831.110201</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>542965726.488891</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>766195145.357583</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>1025133403.89468</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>1212042968.83893</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1178779215.88353</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1109693218.31066</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>1620.31290607613</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>1635.00039276261</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>1638.72346072187</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>1636.45178948466</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>1644.92291198699</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>1625.46421735564</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1602.95130468523</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>1578.87862222441</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>1561.7356332978</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>1586.11898709425</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>1581.89218171183</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>1579.61106848264</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1598.62227324914</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1601.68028328743</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>1585.88767088976</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>1640.34488604704</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>1653.08120513688</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>1657.96893549664</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1656.31901542054</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>1664.81168258819</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>1642.04664356974</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1618.1681544908</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1594.83759360852</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>1581.56093317155</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>1605.43874210356</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>1604.9943663915</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1599.09553420011</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>1617.78175629379</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>1621.06926768452</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>1615.17180044789</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>96725.5237641605</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>102366.696057867</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>101699.771226788</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>104969.377987809</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>107075.320954573</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>110832.788765628</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>100696.185240731</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>106311.677138873</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>130882.297248063</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-11.74</t>
+          <t>159190.879264687</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>170943.424743657</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>192960.40986097</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-13.15</t>
+          <t>226789.430813134</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>248132.595279107</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>181913.166040362</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>2835446343.60454</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>2737810491.09907</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>2762440308.62364</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>2876859901.09354</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>2971875386.78252</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>3247922151.25837</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>2967662374.01092</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>2858221911.67808</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>3071901234.09101</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>3363034395.45219</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>3474921494.18872</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>3656190121.40638</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>3814070099.29394</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>3550593395.81252</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>2713631898.20108</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>75831.3495973377</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>79890.6155496373</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>69.74</t>
+          <t>78082.0581520606</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>83083.1034853668</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>85453.4305373733</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>89747.980114205</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>81785.0223451439</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>85720.0656918854</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>104826.942952039</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>123953.538242074</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>136436.242345256</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>155369.566848147</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>186026.553897001</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>208723.923020259</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>50.13</t>
+          <t>152138.611332661</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6772.82</t>
+          <t>6394675048.33167</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6770.69</t>
+          <t>6247715018.21981</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6703.5</t>
+          <t>5603853531.2329</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6809.79</t>
+          <t>6159276025.18741</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6988.38</t>
+          <t>6512613954.35077</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7061.95</t>
+          <t>7274046918.43544</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7105.7</t>
+          <t>6802796814.27424</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>7006.6</t>
+          <t>6906008317.41889</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6908.1</t>
+          <t>7701027807.71891</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6963.43</t>
+          <t>8276116938.53727</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6979.96</t>
+          <t>8731194337.46579</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>9172389725.59562</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>7319.33</t>
+          <t>9857590170.2604</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>7362.323</t>
+          <t>9433937867.41483</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7146.911</t>
+          <t>7293387923.31672</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6234.64</t>
+          <t>20894.1741668229</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6244.23</t>
+          <t>22476.0805082296</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6174.71</t>
+          <t>23617.7130747272</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6277.92</t>
+          <t>21886.274502442</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6444.15</t>
+          <t>21621.8904171997</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6539.08</t>
+          <t>21084.8086514232</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6609.93</t>
+          <t>18911.1628955872</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6527.4</t>
+          <t>20591.611446988</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6446.22</t>
+          <t>26055.3542960244</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6489.13</t>
+          <t>35237.341022613</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6490.82</t>
+          <t>34507.182398401</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6587.61</t>
+          <t>37590.8430128234</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6822.76</t>
+          <t>40762.8769161332</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6920.38</t>
+          <t>39408.6722588476</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6705.67</t>
+          <t>29774.5547077013</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9880.593</t>
+          <t>-3559228704.72713</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9581.767</t>
+          <t>-3509904527.12074</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9234.511</t>
+          <t>-2841413222.60926</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9599.063</t>
+          <t>-3282416124.09387</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9795.644</t>
+          <t>-3540738567.56826</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10391.999</t>
+          <t>-4026124767.17707</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9833.168</t>
+          <t>-3835134440.26332</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>9592.875</t>
+          <t>-4047786405.74081</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>9999.723</t>
+          <t>-4629126573.6279</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10364.066</t>
+          <t>-4913082543.08509</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10631.977</t>
+          <t>-5256272843.27706</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>10772.474</t>
+          <t>-5516199604.18924</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>11307.814</t>
+          <t>-6043520070.96646</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10209.09</t>
+          <t>-5883344471.60231</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8507.639</t>
+          <t>-4579756025.11564</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>114854.61053</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>122774.93584</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>112054.99439</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>112549.77093</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>113330.15737</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>108058.67783</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>99019.68258</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>110070.99521</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>138070.00793</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>158839.5881</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>160076.10059</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>172003.34448</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>199903.80459</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>208735.56022</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>167415.59572</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3921.84</t>
+          <t>0.0535880004430437</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3903.08</t>
+          <t>0.0446475249065349</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3844.12</t>
+          <t>0.0447102742219196</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3894.96</t>
+          <t>0.0425321401521922</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3973.45</t>
+          <t>0.044700616629324</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4002.83</t>
+          <t>0.0349235375180972</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4037.99</t>
+          <t>0.0276544014955168</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3999.39</t>
+          <t>0.0323535428974781</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3935.33</t>
+          <t>0.0403038827323497</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3950.53</t>
+          <t>0.0547857361478185</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3935.78</t>
+          <t>0.054832707452759</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3934.96</t>
+          <t>0.0666301044100791</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4063.59</t>
+          <t>0.0647866830108882</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4112.632</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3987.768</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>133127.784362746</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>150511.0878089</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>136807.643597456</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>137032.009325101</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>136351.930258648</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>135897.23871761</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>128638.440508168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>140953.50530439</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>174679.259001201</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>198006.744264434</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>201662.713361205</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>211588.521117675</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>248571.027188134</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>262905.781776772</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>222136.709758279</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4836.145</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4955.592</t>
+          <t>161542.668371692</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4248.214</t>
+          <t>147085.249329839</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4634.039</t>
+          <t>147365.163379276</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4766.689</t>
+          <t>146513.806072053</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5239.529</t>
+          <t>145381.994219881</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5334.795</t>
+          <t>136976.405454252</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5490.902</t>
+          <t>149877.465676238</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5875.842</t>
+          <t>185578.561508121</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>6080.401</t>
+          <t>210743.792381888</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>6258.896</t>
+          <t>215298.41297581</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6307.547</t>
+          <t>225476.100933943</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>6691.737</t>
+          <t>264880.656011057</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>6035.202</t>
+          <t>280324.241073704</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>5130.118</t>
+          <t>237231.086161039</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>545298.549566519</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>595671.882688816</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>546296.317448332</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>550559.584078313</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>559827.924355327</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>546059.288310521</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>516590.591712231</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>572674.271663728</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>700425.904121031</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>789646.203294406</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>808590.697184944</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>855373.532513009</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>985730.606451543</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>149845.764626259</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>153009.12433474</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>158833.376482047</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>162872.121386245</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.996</t>
+          <t>178176.232055176</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>190976.721517479</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>196148.574637276</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>198444.141333506</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>204866.178068768</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>215662.279492884</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>220237.056421005</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>233223.897723086</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>236013.372408089</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>228839.713418951</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>133127.784362746</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>139368.926890817</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>142042.186841521</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>147728.752951229</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>151644.686131021</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>166730.278943514</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>179849.433456003</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>185100.922674331</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>187522.568122355</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>193222.90210259</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>201851.287700017</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>207426.50935102</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>220500.176045215</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>223347.6713283</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>215879.258804695</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>77885.4834856216</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>80079.3743283085</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>74998.0413001609</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>75463.020580724</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>79888.9132679466</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>72502.466580119</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>62644.4118557478</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>70534.6420237624</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>90772.7903018787</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107491.992148112</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>109857.58426419</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>124546.720426057</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>140964.435688943</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>150830.402136296</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>116473.816238961</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6234639999.99358</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6244229999.9936</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>6174710000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6277920000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>6444150000.00593</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6539080000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6609930000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6527400000.00494</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6446220000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6489130000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6490820000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6587610000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6822760000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6920380000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6705669998.77628</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6772819999.99282</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6770689999.99285</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6703500000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6809790000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>6988380000.0107</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>7061950000.00911</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7105700000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>7006600000.00862</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6908100000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6963430000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6979960000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>7.072e+09</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>7319330000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>7362323182.22011</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>7146911162.50548</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3921840000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3903080000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3844120000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3894960000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3973450000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4002830000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4037990000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3999390000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3935330000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3950530000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3935780000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3934960000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4063590000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4112632066.22711</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3987768359.95138</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4128899.99999584</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4095799.9999959</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4043200</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4111400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4197700.00000615</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4300700.00000532</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4391200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4393300.00000522</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4367900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4337400</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4348900</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4422500</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4524300</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4541646.26335567</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4424861.28133468</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3847799.99999621</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3819099.99999627</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3768000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3836300</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3917600.00000346</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4022900</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4123600</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4134200.00000303</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4127600</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4091200</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4103200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4170400</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4267900</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4320700</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4228338.56512301</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6772819999.99282</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6770689999.99285</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6703500000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6809790000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6988380000.0107</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>7061950000.00911</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7105700000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>7006600000.00862</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6908100000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6963430000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6979960000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>7.072e+09</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>7319330000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>7362323182.22011</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7146911162.50548</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6234639999.99358</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6244229999.9936</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6174710000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6277920000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>6444150000.00593</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6539080000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6609930000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>6527400000.00494</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6446220000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6489130000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6490820000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6587610000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6822760000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6920380000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6705669998.77628</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.175632394391622</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.178519764421943</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.182521612994752</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.185480918571493</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.199769360570896</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.218077092896323</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.225195429041695</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.231065372362702</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.22077703781729</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.238035604533249</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.249053314488781</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.25943802992654</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.262575913097484</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.27981093651643</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.292918479894697</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.568263560293997</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.574674634470877</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.580260119671008</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.586000513061219</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.574163857675759</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.582930939050782</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.583532617697635</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.584072145887833</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.583415741425941</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.585317212081492</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.581267224553589</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.574570886085595</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.570379798923343</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.561167767493832</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.530134638009854</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.256104045314381</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.24680560110718</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.23721826733424</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.228518568367287</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.226066781753345</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.198991968052896</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.19127195326067</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.184862481749466</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.195807220756769</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.176647183385259</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.16967946095763</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.165991083987865</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.167044287979174</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.159021295989738</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.176946882095448</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.127366819728121</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.129160847897513</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.133416182165984</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.137055627698075</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.1464484811306</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.164891415642487</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.172730142899479</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.176779161263421</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.179782694531231</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.187163260028709</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.198873353722608</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.210336155623757</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.215609489132964</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.230321399524585</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.240881984702742</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.585702966243725</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.591529283873456</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.597372678209279</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.602366870709266</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.594291764382177</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.607277147009464</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.609096810665625</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.610223712014477</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.614762393708153</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.612470415297403</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.609644581664782</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.603618796500982</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.603726782905289</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.598529920241151</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.566309634240847</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.286930214028155</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.279309868229031</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.269211139624737</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.26057750159266</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.259259754487222</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.227831437348049</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.218173046434896</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.212997126722102</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.205454911760616</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.200366324673888</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.19148206461261</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.186045047875261</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.180663727961747</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.171148680234264</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.192808381056411</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>461976.65331</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>501511.41338</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>466168.81334</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>468861.31007</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>476120.03486</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>466126.22559</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>430428.36138</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>466075.03516</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>573860.72027</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>666076.61884</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>694302.57719</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>753739.90604</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>880097.95041</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>949568.28984</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>757060.99647</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>221026.57373</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>241622.0427</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>222083.29063</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>222828.18396</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>226402.71934</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>217884.4608</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>199620.81731</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>220412.1077</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>276351.35181</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>318235.78453</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>325155.99724</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>350022.82136</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>405845.0917</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>431154.64321</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>353704.9024</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3883063.05764445</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4018765.57132922</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4144897.71115209</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4291173.96676717</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4451909.0550342</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4621620.99180891</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4765026.77031318</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4883940.32262649</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5000945.27065932</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5138989.3150617</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5306922.67425119</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5502674.76391365</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5725293.18762794</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
